--- a/artfynd/A 12279-2026 artfynd.xlsx
+++ b/artfynd/A 12279-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135804116</v>
       </c>
       <c r="B2" t="n">
-        <v>98130</v>
+        <v>98132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12279-2026 artfynd.xlsx
+++ b/artfynd/A 12279-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135804116</v>
       </c>
       <c r="B2" t="n">
-        <v>98132</v>
+        <v>98149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12279-2026 artfynd.xlsx
+++ b/artfynd/A 12279-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135804116</v>
       </c>
       <c r="B2" t="n">
-        <v>98149</v>
+        <v>98150</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12279-2026 artfynd.xlsx
+++ b/artfynd/A 12279-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135804116</v>
       </c>
       <c r="B2" t="n">
-        <v>98150</v>
+        <v>98151</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12279-2026 artfynd.xlsx
+++ b/artfynd/A 12279-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135804116</v>
       </c>
       <c r="B2" t="n">
-        <v>98151</v>
+        <v>98152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12279-2026 artfynd.xlsx
+++ b/artfynd/A 12279-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135804116</v>
       </c>
       <c r="B2" t="n">
-        <v>98152</v>
+        <v>98158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12279-2026 artfynd.xlsx
+++ b/artfynd/A 12279-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135804116</v>
       </c>
       <c r="B2" t="n">
-        <v>98158</v>
+        <v>98159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
